--- a/CJFAS-Submission/Tables/Table1.xlsx
+++ b/CJFAS-Submission/Tables/Table1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rames\Documents\CHUMputerVisionProject\ManuscriptSubmission\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rames\Documents\GitHub\chumputer-manuscript\CJFAS-Submission\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8537A7-5DCC-4345-BBD4-E2087B383813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73EC0D3F-0BED-44AD-9D9E-B3BAD39FA690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31515" yWindow="3555" windowWidth="23415" windowHeight="16860" xr2:uid="{AEB08D76-C810-40CC-B74C-D2C05A209B30}"/>
+    <workbookView xWindow="3330" yWindow="1770" windowWidth="21600" windowHeight="11295" xr2:uid="{AEB08D76-C810-40CC-B74C-D2C05A209B30}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -66,16 +66,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -94,6 +90,13 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -128,35 +131,37 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -492,334 +497,337 @@
   <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="9.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="9" width="8.140625" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="5"/>
+    </row>
+    <row r="2" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5">
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
         <v>2</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="2">
         <v>3</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="2">
         <v>4</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="2">
         <v>5</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="2">
         <v>6</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="2">
         <v>7</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
         <v>16</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="3">
         <v>26208</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="3">
         <v>23873</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="3">
         <v>143</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8">
+      <c r="I3" s="3"/>
+      <c r="J3" s="4">
         <v>50241</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="7">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
         <v>144</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="3">
         <v>3748</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="3">
         <v>7355</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="3">
         <v>1254</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="3">
         <v>110</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="3">
         <v>5</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="4">
         <v>12617</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="3">
         <v>207</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>34</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="3">
         <v>4</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="3">
         <v>431</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="3">
         <v>1963</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="3">
         <v>51</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="3">
         <v>8</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="4">
         <v>2698</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3">
         <v>241</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="3">
         <v>278</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="3">
         <v>71</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="3">
         <v>7</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="8">
+      <c r="I6" s="3"/>
+      <c r="J6" s="4">
         <v>597</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
-      <c r="B7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
         <v>208</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>179</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="3">
         <v>4009</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="3">
         <v>34272</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="3">
         <v>27161</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="3">
         <v>311</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="3">
         <v>13</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="4">
         <v>66153</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
         <v>16</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="3">
         <v>2487</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="3">
         <v>3447</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="3">
         <v>142</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="8">
+      <c r="I8" s="3"/>
+      <c r="J8" s="4">
         <v>6093</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
         <v>88</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="3">
         <v>3720</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="3">
         <v>3333</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="3">
         <v>1249</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="3">
         <v>83</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="3">
         <v>5</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="4">
         <v>8479</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="3">
         <v>178</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="3">
         <v>29</v>
       </c>
-      <c r="E10" s="7">
-        <v>1</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
         <v>5</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="3">
         <v>382</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="3">
         <v>16</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="3">
         <v>6</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="4">
         <v>617</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3">
         <v>224</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="3">
         <v>270</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="3">
         <v>64</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="3">
         <v>7</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8">
+      <c r="I11" s="3"/>
+      <c r="J11" s="4">
         <v>565</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
-      <c r="B12" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="7">
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
         <v>179</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="3">
         <v>118</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="3">
         <v>3961</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="3">
         <v>6095</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="3">
         <v>5142</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="3">
         <v>248</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="3">
         <v>11</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="4">
         <v>15754</v>
       </c>
     </row>

--- a/CJFAS-Submission/Tables/Table1.xlsx
+++ b/CJFAS-Submission/Tables/Table1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rames\Documents\GitHub\chumputer-manuscript\CJFAS-Submission\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73EC0D3F-0BED-44AD-9D9E-B3BAD39FA690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6836A288-C6E5-4A82-BE42-E91E9ED83199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="1770" windowWidth="21600" windowHeight="11295" xr2:uid="{AEB08D76-C810-40CC-B74C-D2C05A209B30}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2068ED51-EF85-422D-A9BF-82A8376C1671}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,27 +36,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
-  <si>
-    <t xml:space="preserve">Agency </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+  <si>
+    <r>
+      <t>Preprocessing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Consensus age reader decision</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t>ADF&amp;G</t>
-  </si>
-  <si>
-    <t>NOAA</t>
-  </si>
-  <si>
-    <t>DFO</t>
-  </si>
-  <si>
-    <t>NSRAA</t>
-  </si>
-  <si>
-    <t>Model</t>
+    <t>SAM</t>
+  </si>
+  <si>
+    <t>Original correct</t>
+  </si>
+  <si>
+    <t>Model correct</t>
+  </si>
+  <si>
+    <t>Neither</t>
+  </si>
+  <si>
+    <t>Ambiguous</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>YOLO</t>
   </si>
   <si>
     <t>Age Label</t>
@@ -66,11 +86,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-  </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,13 +106,6 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -131,11 +140,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -143,16 +151,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -160,8 +174,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -493,349 +506,322 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEDCD52-0B92-4746-97DB-2ABF488B8008}">
-  <dimension ref="A1:J12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DC6A64C-1C0F-4884-ACD2-20A2F3822E1F}">
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="9" width="8.140625" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="8" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="7" t="s">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4">
+        <v>21</v>
+      </c>
+      <c r="F3" s="4">
+        <v>15</v>
+      </c>
+      <c r="G3" s="4">
+        <v>4</v>
+      </c>
+      <c r="H3" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4">
+        <v>17</v>
+      </c>
+      <c r="E4" s="4">
+        <v>24</v>
+      </c>
+      <c r="F4" s="4">
+        <v>26</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="C6" s="4">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4">
+        <v>11</v>
+      </c>
+      <c r="E6" s="4">
+        <v>9</v>
+      </c>
+      <c r="F6" s="4">
+        <v>26</v>
+      </c>
+      <c r="G6" s="4">
+        <v>10</v>
+      </c>
+      <c r="H6" s="5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4">
         <v>1</v>
       </c>
-      <c r="D2" s="2">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="D7" s="4">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6">
+        <v>14</v>
+      </c>
+      <c r="D8" s="6">
+        <v>34</v>
+      </c>
+      <c r="E8" s="6">
+        <v>54</v>
+      </c>
+      <c r="F8" s="6">
+        <v>68</v>
+      </c>
+      <c r="G8" s="6">
+        <v>16</v>
+      </c>
+      <c r="H8" s="7">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="4">
+        <v>10</v>
+      </c>
+      <c r="D9" s="4">
+        <v>21</v>
+      </c>
+      <c r="E9" s="4">
+        <v>26</v>
+      </c>
+      <c r="F9" s="4">
+        <v>23</v>
+      </c>
+      <c r="G9" s="4">
         <v>3</v>
       </c>
-      <c r="F2" s="2">
+      <c r="H9" s="5">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4">
+        <v>17</v>
+      </c>
+      <c r="E10" s="4">
+        <v>24</v>
+      </c>
+      <c r="F10" s="4">
+        <v>24</v>
+      </c>
+      <c r="G10" s="4">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2</v>
+      </c>
+      <c r="D12" s="4">
+        <v>17</v>
+      </c>
+      <c r="E12" s="4">
+        <v>10</v>
+      </c>
+      <c r="F12" s="4">
+        <v>30</v>
+      </c>
+      <c r="G12" s="4">
+        <v>11</v>
+      </c>
+      <c r="H12" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="5">
         <v>4</v>
       </c>
-      <c r="G2" s="2">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2">
-        <v>7</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
+    </row>
+    <row r="14" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="6">
+        <v>15</v>
+      </c>
+      <c r="D14" s="6">
+        <v>57</v>
+      </c>
+      <c r="E14" s="6">
+        <v>60</v>
+      </c>
+      <c r="F14" s="6">
+        <v>79</v>
+      </c>
+      <c r="G14" s="6">
         <v>16</v>
       </c>
-      <c r="F3" s="3">
-        <v>26208</v>
-      </c>
-      <c r="G3" s="3">
-        <v>23873</v>
-      </c>
-      <c r="H3" s="3">
-        <v>143</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="4">
-        <v>50241</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>144</v>
-      </c>
-      <c r="E4" s="3">
-        <v>3748</v>
-      </c>
-      <c r="F4" s="3">
-        <v>7355</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1254</v>
-      </c>
-      <c r="H4" s="3">
-        <v>110</v>
-      </c>
-      <c r="I4" s="3">
-        <v>5</v>
-      </c>
-      <c r="J4" s="4">
-        <v>12617</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3">
-        <v>207</v>
-      </c>
-      <c r="D5" s="3">
-        <v>34</v>
-      </c>
-      <c r="E5" s="3">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3">
-        <v>431</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1963</v>
-      </c>
-      <c r="H5" s="3">
-        <v>51</v>
-      </c>
-      <c r="I5" s="3">
-        <v>8</v>
-      </c>
-      <c r="J5" s="4">
-        <v>2698</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3">
-        <v>241</v>
-      </c>
-      <c r="F6" s="3">
-        <v>278</v>
-      </c>
-      <c r="G6" s="3">
-        <v>71</v>
-      </c>
-      <c r="H6" s="3">
-        <v>7</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="4">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3">
-        <v>208</v>
-      </c>
-      <c r="D7" s="3">
-        <v>179</v>
-      </c>
-      <c r="E7" s="3">
-        <v>4009</v>
-      </c>
-      <c r="F7" s="3">
-        <v>34272</v>
-      </c>
-      <c r="G7" s="3">
-        <v>27161</v>
-      </c>
-      <c r="H7" s="3">
-        <v>311</v>
-      </c>
-      <c r="I7" s="3">
-        <v>13</v>
-      </c>
-      <c r="J7" s="4">
-        <v>66153</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>16</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2487</v>
-      </c>
-      <c r="G8" s="3">
-        <v>3447</v>
-      </c>
-      <c r="H8" s="3">
-        <v>142</v>
-      </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="4">
-        <v>6093</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3">
-        <v>88</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3720</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3333</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1249</v>
-      </c>
-      <c r="H9" s="3">
-        <v>83</v>
-      </c>
-      <c r="I9" s="3">
-        <v>5</v>
-      </c>
-      <c r="J9" s="4">
-        <v>8479</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3">
-        <v>178</v>
-      </c>
-      <c r="D10" s="3">
-        <v>29</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3">
-        <v>382</v>
-      </c>
-      <c r="H10" s="3">
-        <v>16</v>
-      </c>
-      <c r="I10" s="3">
-        <v>6</v>
-      </c>
-      <c r="J10" s="4">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3">
-        <v>224</v>
-      </c>
-      <c r="F11" s="3">
-        <v>270</v>
-      </c>
-      <c r="G11" s="3">
-        <v>64</v>
-      </c>
-      <c r="H11" s="3">
-        <v>7</v>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="4">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3">
-        <v>179</v>
-      </c>
-      <c r="D12" s="3">
-        <v>118</v>
-      </c>
-      <c r="E12" s="3">
-        <v>3961</v>
-      </c>
-      <c r="F12" s="3">
-        <v>6095</v>
-      </c>
-      <c r="G12" s="3">
-        <v>5142</v>
-      </c>
-      <c r="H12" s="3">
-        <v>248</v>
-      </c>
-      <c r="I12" s="3">
-        <v>11</v>
-      </c>
-      <c r="J12" s="4">
-        <v>15754</v>
+      <c r="H14" s="7">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="C1:I1"/>
+  <mergeCells count="1">
+    <mergeCell ref="C1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CJFAS-Submission/Tables/Table1.xlsx
+++ b/CJFAS-Submission/Tables/Table1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rames\Documents\GitHub\chumputer-manuscript\CJFAS-Submission\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6836A288-C6E5-4A82-BE42-E91E9ED83199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88431834-136C-4599-817D-F57FBE512796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2068ED51-EF85-422D-A9BF-82A8376C1671}"/>
+    <workbookView xWindow="6060" yWindow="1395" windowWidth="46935" windowHeight="21495" xr2:uid="{2068ED51-EF85-422D-A9BF-82A8376C1671}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,12 +61,6 @@
     <t>SAM</t>
   </si>
   <si>
-    <t>Original correct</t>
-  </si>
-  <si>
-    <t>Model correct</t>
-  </si>
-  <si>
     <t>Neither</t>
   </si>
   <si>
@@ -80,6 +74,12 @@
   </si>
   <si>
     <t>Age Label</t>
+  </si>
+  <si>
+    <t>Original supported</t>
+  </si>
+  <si>
+    <t>Model supported</t>
   </si>
 </sst>
 </file>
@@ -519,7 +519,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
@@ -558,7 +558,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" s="4">
         <v>8</v>
@@ -582,7 +582,7 @@
     <row r="4" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4">
         <v>2</v>
@@ -606,7 +606,7 @@
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -618,7 +618,7 @@
     <row r="6" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="4">
         <v>3</v>
@@ -642,7 +642,7 @@
     <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="9" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="C9" s="4">
         <v>10</v>
@@ -714,7 +714,7 @@
     <row r="10" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4">
         <v>2</v>
@@ -738,7 +738,7 @@
     <row r="11" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -754,7 +754,7 @@
     <row r="12" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12" s="4">
         <v>2</v>
@@ -778,7 +778,7 @@
     <row r="13" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C13" s="4">
         <v>1</v>
